--- a/controles/attribuutkenmerkwijzigingen.xlsx
+++ b/controles/attribuutkenmerkwijzigingen.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PieterBresters\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtinggeonovum.sharepoint.com/sites/msteams_fad46a/Gedeelde documenten/General/4 Werkdossier/Wijzigingsvoorstellen/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F3AB6F-7286-45DD-B066-1C23A22D7238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{D7F3AB6F-7286-45DD-B066-1C23A22D7238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7434B8DA-54BB-4F66-B81D-3E4538446477}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D12776E7-BC12-4242-A1C7-07D171B3E3CA}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="191">
   <si>
     <t>klasse</t>
   </si>
@@ -605,9 +605,6 @@
     <t>meeteenheid km/u</t>
   </si>
   <si>
-    <t>meeteenheid km/u en min wordt 0</t>
-  </si>
-  <si>
     <t>geen</t>
   </si>
   <si>
@@ -618,6 +615,12 @@
   </si>
   <si>
     <t>meeteenheid aantal</t>
+  </si>
+  <si>
+    <t>meeteenheid km/u en min -&gt; 0, max -&gt;999</t>
+  </si>
+  <si>
+    <t>maxwaarde wordt 99.9 (ook in patroon)</t>
   </si>
 </sst>
 </file>
@@ -653,9 +656,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -702,6 +704,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1045,16 +1051,16 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.5546875" customWidth="1"/>
+    <col min="2" max="2" width="48.77734375" customWidth="1"/>
     <col min="3" max="3" width="25.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="76.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="6" max="6" width="80.33203125" customWidth="1"/>
+    <col min="7" max="7" width="8.77734375" customWidth="1"/>
     <col min="8" max="8" width="7.21875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.5546875" customWidth="1"/>
-    <col min="10" max="10" width="38.21875" customWidth="1"/>
-    <col min="11" max="11" width="8.88671875" customWidth="1"/>
+    <col min="10" max="10" width="38.77734375" customWidth="1"/>
+    <col min="11" max="11" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -1120,10 +1126,10 @@
       <c r="I2">
         <v>999</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" t="s">
         <v>173</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" t="s">
         <v>172</v>
       </c>
     </row>
@@ -1155,10 +1161,10 @@
       <c r="I3">
         <v>1</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="K3" s="1" t="s">
+      <c r="J3" t="s">
+        <v>186</v>
+      </c>
+      <c r="K3" t="s">
         <v>172</v>
       </c>
     </row>
@@ -1190,10 +1196,10 @@
       <c r="I4">
         <v>1</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="K4" s="1" t="s">
+      <c r="J4" t="s">
+        <v>186</v>
+      </c>
+      <c r="K4" t="s">
         <v>172</v>
       </c>
     </row>
@@ -1225,10 +1231,10 @@
       <c r="I5">
         <v>1</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="K5" s="1" t="s">
+      <c r="J5" t="s">
+        <v>186</v>
+      </c>
+      <c r="K5" t="s">
         <v>172</v>
       </c>
     </row>
@@ -1260,10 +1266,10 @@
       <c r="I6">
         <v>1</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="K6" s="1" t="s">
+      <c r="J6" t="s">
+        <v>186</v>
+      </c>
+      <c r="K6" t="s">
         <v>172</v>
       </c>
     </row>
@@ -1295,10 +1301,10 @@
       <c r="I7">
         <v>1</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="K7" s="1" t="s">
+      <c r="J7" t="s">
+        <v>186</v>
+      </c>
+      <c r="K7" t="s">
         <v>172</v>
       </c>
     </row>
@@ -1330,10 +1336,10 @@
       <c r="I8">
         <v>1</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="K8" s="1" t="s">
+      <c r="J8" t="s">
+        <v>186</v>
+      </c>
+      <c r="K8" t="s">
         <v>172</v>
       </c>
     </row>
@@ -1365,10 +1371,10 @@
       <c r="I9">
         <v>1</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="K9" s="1" t="s">
+      <c r="J9" t="s">
+        <v>186</v>
+      </c>
+      <c r="K9" t="s">
         <v>172</v>
       </c>
     </row>
@@ -1400,10 +1406,10 @@
       <c r="I10">
         <v>1</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="K10" s="1" t="s">
+      <c r="J10" t="s">
+        <v>186</v>
+      </c>
+      <c r="K10" t="s">
         <v>172</v>
       </c>
     </row>
@@ -1435,10 +1441,10 @@
       <c r="I11">
         <v>1</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="K11" s="1" t="s">
+      <c r="J11" t="s">
+        <v>186</v>
+      </c>
+      <c r="K11" t="s">
         <v>172</v>
       </c>
     </row>
@@ -1470,10 +1476,10 @@
       <c r="I12">
         <v>360</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="J12" t="s">
         <v>173</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="K12" t="s">
         <v>172</v>
       </c>
     </row>
@@ -1505,10 +1511,10 @@
       <c r="I13">
         <v>360</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="J13" t="s">
         <v>173</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="K13" t="s">
         <v>172</v>
       </c>
     </row>
@@ -1540,10 +1546,10 @@
       <c r="I14">
         <v>99999</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" t="s">
         <v>174</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="K14" t="s">
         <v>175</v>
       </c>
     </row>
@@ -1575,10 +1581,10 @@
       <c r="I15">
         <v>99999</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="J15" t="s">
         <v>174</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="K15" t="s">
         <v>175</v>
       </c>
     </row>
@@ -1610,10 +1616,10 @@
       <c r="I16">
         <v>99999</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J16" t="s">
         <v>174</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="K16" t="s">
         <v>175</v>
       </c>
     </row>
@@ -1645,10 +1651,10 @@
       <c r="I17">
         <v>99999</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="J17" t="s">
         <v>174</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="K17" t="s">
         <v>175</v>
       </c>
     </row>
@@ -1680,10 +1686,10 @@
       <c r="I18">
         <v>99999</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="J18" t="s">
         <v>174</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="K18" t="s">
         <v>175</v>
       </c>
     </row>
@@ -1715,10 +1721,10 @@
       <c r="I19">
         <v>99999</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="J19" t="s">
         <v>174</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="K19" t="s">
         <v>175</v>
       </c>
     </row>
@@ -1750,10 +1756,10 @@
       <c r="I20">
         <v>99999</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="J20" t="s">
         <v>174</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="K20" t="s">
         <v>175</v>
       </c>
     </row>
@@ -1785,10 +1791,10 @@
       <c r="I21">
         <v>99999</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="J21" t="s">
         <v>174</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="K21" t="s">
         <v>175</v>
       </c>
     </row>
@@ -1820,10 +1826,10 @@
       <c r="I22">
         <v>99999</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="J22" t="s">
         <v>174</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="K22" t="s">
         <v>175</v>
       </c>
     </row>
@@ -1855,10 +1861,10 @@
       <c r="I23">
         <v>1999</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="J23" t="s">
         <v>176</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="K23" t="s">
         <v>175</v>
       </c>
     </row>
@@ -1890,10 +1896,10 @@
       <c r="I24">
         <v>1</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="J24" t="s">
         <v>177</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="K24" t="s">
         <v>172</v>
       </c>
     </row>
@@ -1922,10 +1928,10 @@
       <c r="H25" t="s">
         <v>14</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="J25" t="s">
         <v>171</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="K25" t="s">
         <v>172</v>
       </c>
     </row>
@@ -1954,10 +1960,10 @@
       <c r="H26" t="s">
         <v>14</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="J26" t="s">
         <v>170</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="K26" t="s">
         <v>172</v>
       </c>
     </row>
@@ -1989,10 +1995,10 @@
       <c r="I27">
         <v>1</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="J27" t="s">
         <v>178</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="K27" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2021,10 +2027,10 @@
       <c r="H28" t="s">
         <v>14</v>
       </c>
-      <c r="J28" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="K28" s="1" t="s">
+      <c r="J28" t="s">
+        <v>185</v>
+      </c>
+      <c r="K28" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2056,10 +2062,10 @@
       <c r="I29">
         <v>99</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="J29" t="s">
         <v>173</v>
       </c>
-      <c r="K29" s="1" t="s">
+      <c r="K29" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2088,10 +2094,10 @@
       <c r="H30" t="s">
         <v>14</v>
       </c>
-      <c r="J30" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="K30" s="1" t="s">
+      <c r="J30" t="s">
+        <v>185</v>
+      </c>
+      <c r="K30" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2120,10 +2126,10 @@
       <c r="H31" t="s">
         <v>16</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="J31" t="s">
         <v>173</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="K31" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2155,10 +2161,10 @@
       <c r="I32">
         <v>1000</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="J32" t="s">
         <v>173</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="K32" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2190,10 +2196,10 @@
       <c r="I33">
         <v>1</v>
       </c>
-      <c r="J33" s="1" t="s">
+      <c r="J33" t="s">
         <v>178</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="K33" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2225,10 +2231,10 @@
       <c r="I34">
         <v>1</v>
       </c>
-      <c r="J34" s="1" t="s">
+      <c r="J34" t="s">
         <v>178</v>
       </c>
-      <c r="K34" s="1" t="s">
+      <c r="K34" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2260,10 +2266,10 @@
       <c r="I35">
         <v>1</v>
       </c>
-      <c r="J35" s="1" t="s">
+      <c r="J35" t="s">
         <v>178</v>
       </c>
-      <c r="K35" s="1" t="s">
+      <c r="K35" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2295,10 +2301,10 @@
       <c r="I36">
         <v>99</v>
       </c>
-      <c r="J36" s="1" t="s">
+      <c r="J36" t="s">
         <v>180</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="K36" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2330,10 +2336,10 @@
       <c r="I37">
         <v>45</v>
       </c>
-      <c r="J37" s="1" t="s">
+      <c r="J37" t="s">
         <v>173</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="K37" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2365,10 +2371,10 @@
       <c r="I38">
         <v>999</v>
       </c>
-      <c r="J38" s="1" t="s">
+      <c r="J38" t="s">
         <v>173</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="K38" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2400,10 +2406,10 @@
       <c r="I39">
         <v>999</v>
       </c>
-      <c r="J39" s="1" t="s">
+      <c r="J39" t="s">
         <v>173</v>
       </c>
-      <c r="K39" s="1" t="s">
+      <c r="K39" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2432,10 +2438,10 @@
       <c r="H40" t="s">
         <v>14</v>
       </c>
-      <c r="J40" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="K40" s="1" t="s">
+      <c r="J40" t="s">
+        <v>185</v>
+      </c>
+      <c r="K40" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2467,10 +2473,10 @@
       <c r="I41">
         <v>999</v>
       </c>
-      <c r="J41" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="K41" s="1" t="s">
+      <c r="J41" t="s">
+        <v>190</v>
+      </c>
+      <c r="K41" t="s">
         <v>175</v>
       </c>
     </row>
@@ -2502,10 +2508,10 @@
       <c r="I42">
         <v>999</v>
       </c>
-      <c r="J42" s="1" t="s">
+      <c r="J42" t="s">
         <v>173</v>
       </c>
-      <c r="K42" s="1" t="s">
+      <c r="K42" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2537,10 +2543,10 @@
       <c r="I43">
         <v>45</v>
       </c>
-      <c r="J43" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="K43" s="1" t="s">
+      <c r="J43" t="s">
+        <v>185</v>
+      </c>
+      <c r="K43" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2569,10 +2575,10 @@
       <c r="H44" t="s">
         <v>14</v>
       </c>
-      <c r="J44" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="K44" s="1" t="s">
+      <c r="J44" t="s">
+        <v>185</v>
+      </c>
+      <c r="K44" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2604,10 +2610,10 @@
       <c r="I45">
         <v>45</v>
       </c>
-      <c r="J45" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="K45" s="1" t="s">
+      <c r="J45" t="s">
+        <v>185</v>
+      </c>
+      <c r="K45" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2636,10 +2642,10 @@
       <c r="H46" t="s">
         <v>14</v>
       </c>
-      <c r="J46" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="K46" s="1" t="s">
+      <c r="J46" t="s">
+        <v>185</v>
+      </c>
+      <c r="K46" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2671,10 +2677,10 @@
       <c r="I47">
         <v>1</v>
       </c>
-      <c r="J47" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="K47" s="1" t="s">
+      <c r="J47" t="s">
+        <v>187</v>
+      </c>
+      <c r="K47" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2706,10 +2712,10 @@
       <c r="I48">
         <v>1999</v>
       </c>
-      <c r="J48" s="1" t="s">
+      <c r="J48" t="s">
         <v>181</v>
       </c>
-      <c r="K48" s="1" t="s">
+      <c r="K48" t="s">
         <v>175</v>
       </c>
     </row>
@@ -2741,10 +2747,10 @@
       <c r="I49">
         <v>999</v>
       </c>
-      <c r="J49" s="1" t="s">
+      <c r="J49" t="s">
         <v>179</v>
       </c>
-      <c r="K49" s="1" t="s">
+      <c r="K49" t="s">
         <v>175</v>
       </c>
     </row>
@@ -2776,10 +2782,10 @@
       <c r="I50">
         <v>99999</v>
       </c>
-      <c r="J50" s="1" t="s">
+      <c r="J50" t="s">
         <v>183</v>
       </c>
-      <c r="K50" s="1" t="s">
+      <c r="K50" t="s">
         <v>182</v>
       </c>
     </row>
@@ -2808,10 +2814,10 @@
       <c r="H51" t="s">
         <v>14</v>
       </c>
-      <c r="J51" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="K51" s="1" t="s">
+      <c r="J51" t="s">
+        <v>185</v>
+      </c>
+      <c r="K51" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2840,10 +2846,10 @@
       <c r="H52" t="s">
         <v>100</v>
       </c>
-      <c r="J52" s="1" t="s">
+      <c r="J52" t="s">
         <v>173</v>
       </c>
-      <c r="K52" s="1" t="s">
+      <c r="K52" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2872,10 +2878,10 @@
       <c r="H53" t="s">
         <v>14</v>
       </c>
-      <c r="J53" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="K53" s="1" t="s">
+      <c r="J53" t="s">
+        <v>185</v>
+      </c>
+      <c r="K53" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2907,10 +2913,10 @@
       <c r="I54">
         <v>999</v>
       </c>
-      <c r="J54" s="1" t="s">
+      <c r="J54" t="s">
         <v>173</v>
       </c>
-      <c r="K54" s="1" t="s">
+      <c r="K54" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2942,10 +2948,10 @@
       <c r="I55">
         <v>999</v>
       </c>
-      <c r="J55" s="1" t="s">
+      <c r="J55" t="s">
         <v>173</v>
       </c>
-      <c r="K55" s="1" t="s">
+      <c r="K55" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2977,10 +2983,10 @@
       <c r="I56">
         <v>999</v>
       </c>
-      <c r="J56" s="1" t="s">
+      <c r="J56" t="s">
         <v>173</v>
       </c>
-      <c r="K56" s="1" t="s">
+      <c r="K56" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3012,10 +3018,10 @@
       <c r="I57">
         <v>999</v>
       </c>
-      <c r="J57" s="1" t="s">
+      <c r="J57" t="s">
         <v>173</v>
       </c>
-      <c r="K57" s="1" t="s">
+      <c r="K57" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3047,10 +3053,10 @@
       <c r="I58">
         <v>999</v>
       </c>
-      <c r="J58" s="1" t="s">
+      <c r="J58" t="s">
         <v>173</v>
       </c>
-      <c r="K58" s="1" t="s">
+      <c r="K58" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3082,10 +3088,10 @@
       <c r="I59">
         <v>999</v>
       </c>
-      <c r="J59" s="1" t="s">
+      <c r="J59" t="s">
         <v>173</v>
       </c>
-      <c r="K59" s="1" t="s">
+      <c r="K59" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3117,10 +3123,10 @@
       <c r="I60">
         <v>999</v>
       </c>
-      <c r="J60" s="1" t="s">
+      <c r="J60" t="s">
         <v>173</v>
       </c>
-      <c r="K60" s="1" t="s">
+      <c r="K60" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3152,10 +3158,10 @@
       <c r="I61">
         <v>999</v>
       </c>
-      <c r="J61" s="1" t="s">
+      <c r="J61" t="s">
         <v>173</v>
       </c>
-      <c r="K61" s="1" t="s">
+      <c r="K61" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3187,10 +3193,10 @@
       <c r="I62">
         <v>999</v>
       </c>
-      <c r="J62" s="1" t="s">
+      <c r="J62" t="s">
         <v>173</v>
       </c>
-      <c r="K62" s="1" t="s">
+      <c r="K62" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3222,10 +3228,10 @@
       <c r="I63">
         <v>999</v>
       </c>
-      <c r="J63" s="1" t="s">
+      <c r="J63" t="s">
         <v>173</v>
       </c>
-      <c r="K63" s="1" t="s">
+      <c r="K63" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3257,10 +3263,10 @@
       <c r="I64">
         <v>999</v>
       </c>
-      <c r="J64" s="1" t="s">
+      <c r="J64" t="s">
         <v>173</v>
       </c>
-      <c r="K64" s="1" t="s">
+      <c r="K64" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3292,10 +3298,10 @@
       <c r="I65">
         <v>999</v>
       </c>
-      <c r="J65" s="1" t="s">
+      <c r="J65" t="s">
         <v>173</v>
       </c>
-      <c r="K65" s="1" t="s">
+      <c r="K65" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3327,10 +3333,10 @@
       <c r="I66">
         <v>999</v>
       </c>
-      <c r="J66" s="1" t="s">
+      <c r="J66" t="s">
         <v>173</v>
       </c>
-      <c r="K66" s="1" t="s">
+      <c r="K66" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3362,10 +3368,10 @@
       <c r="I67">
         <v>999</v>
       </c>
-      <c r="J67" s="1" t="s">
+      <c r="J67" t="s">
         <v>173</v>
       </c>
-      <c r="K67" s="1" t="s">
+      <c r="K67" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3397,10 +3403,10 @@
       <c r="I68">
         <v>999</v>
       </c>
-      <c r="J68" s="1" t="s">
+      <c r="J68" t="s">
         <v>173</v>
       </c>
-      <c r="K68" s="1" t="s">
+      <c r="K68" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3432,10 +3438,10 @@
       <c r="I69">
         <v>999</v>
       </c>
-      <c r="J69" s="1" t="s">
+      <c r="J69" t="s">
         <v>173</v>
       </c>
-      <c r="K69" s="1" t="s">
+      <c r="K69" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3467,10 +3473,10 @@
       <c r="I70">
         <v>999</v>
       </c>
-      <c r="J70" s="1" t="s">
+      <c r="J70" t="s">
         <v>173</v>
       </c>
-      <c r="K70" s="1" t="s">
+      <c r="K70" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3502,10 +3508,10 @@
       <c r="I71">
         <v>999</v>
       </c>
-      <c r="J71" s="1" t="s">
+      <c r="J71" t="s">
         <v>173</v>
       </c>
-      <c r="K71" s="1" t="s">
+      <c r="K71" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3537,10 +3543,10 @@
       <c r="I72">
         <v>999</v>
       </c>
-      <c r="J72" s="1" t="s">
+      <c r="J72" t="s">
         <v>173</v>
       </c>
-      <c r="K72" s="1" t="s">
+      <c r="K72" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3572,10 +3578,10 @@
       <c r="I73">
         <v>999</v>
       </c>
-      <c r="J73" s="1" t="s">
+      <c r="J73" t="s">
         <v>173</v>
       </c>
-      <c r="K73" s="1" t="s">
+      <c r="K73" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3607,10 +3613,10 @@
       <c r="I74">
         <v>999</v>
       </c>
-      <c r="J74" s="1" t="s">
+      <c r="J74" t="s">
         <v>173</v>
       </c>
-      <c r="K74" s="1" t="s">
+      <c r="K74" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3642,10 +3648,10 @@
       <c r="I75">
         <v>999</v>
       </c>
-      <c r="J75" s="1" t="s">
+      <c r="J75" t="s">
         <v>173</v>
       </c>
-      <c r="K75" s="1" t="s">
+      <c r="K75" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3677,10 +3683,10 @@
       <c r="I76">
         <v>999</v>
       </c>
-      <c r="J76" s="1" t="s">
+      <c r="J76" t="s">
         <v>173</v>
       </c>
-      <c r="K76" s="1" t="s">
+      <c r="K76" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3712,10 +3718,10 @@
       <c r="I77">
         <v>999</v>
       </c>
-      <c r="J77" s="1" t="s">
+      <c r="J77" t="s">
         <v>173</v>
       </c>
-      <c r="K77" s="1" t="s">
+      <c r="K77" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3747,10 +3753,10 @@
       <c r="I78">
         <v>999</v>
       </c>
-      <c r="J78" s="1" t="s">
+      <c r="J78" t="s">
         <v>173</v>
       </c>
-      <c r="K78" s="1" t="s">
+      <c r="K78" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3782,10 +3788,10 @@
       <c r="I79">
         <v>999</v>
       </c>
-      <c r="J79" s="1" t="s">
+      <c r="J79" t="s">
         <v>173</v>
       </c>
-      <c r="K79" s="1" t="s">
+      <c r="K79" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3817,10 +3823,10 @@
       <c r="I80">
         <v>999</v>
       </c>
-      <c r="J80" s="1" t="s">
+      <c r="J80" t="s">
         <v>173</v>
       </c>
-      <c r="K80" s="1" t="s">
+      <c r="K80" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3852,10 +3858,10 @@
       <c r="I81">
         <v>999</v>
       </c>
-      <c r="J81" s="1" t="s">
+      <c r="J81" t="s">
         <v>173</v>
       </c>
-      <c r="K81" s="1" t="s">
+      <c r="K81" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3887,10 +3893,10 @@
       <c r="I82">
         <v>999</v>
       </c>
-      <c r="J82" s="1" t="s">
+      <c r="J82" t="s">
         <v>173</v>
       </c>
-      <c r="K82" s="1" t="s">
+      <c r="K82" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3919,10 +3925,10 @@
       <c r="H83" t="s">
         <v>14</v>
       </c>
-      <c r="J83" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="K83" s="1" t="s">
+      <c r="J83" t="s">
+        <v>185</v>
+      </c>
+      <c r="K83" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3954,10 +3960,10 @@
       <c r="I84">
         <v>99</v>
       </c>
-      <c r="J84" s="1" t="s">
+      <c r="J84" t="s">
         <v>173</v>
       </c>
-      <c r="K84" s="1" t="s">
+      <c r="K84" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3989,10 +3995,10 @@
       <c r="I85">
         <v>9999</v>
       </c>
-      <c r="J85" s="1" t="s">
+      <c r="J85" t="s">
         <v>173</v>
       </c>
-      <c r="K85" s="1" t="s">
+      <c r="K85" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4021,10 +4027,10 @@
       <c r="H86" t="s">
         <v>14</v>
       </c>
-      <c r="J86" s="1" t="s">
+      <c r="J86" t="s">
         <v>170</v>
       </c>
-      <c r="K86" s="1" t="s">
+      <c r="K86" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4056,10 +4062,10 @@
       <c r="I87">
         <v>99999</v>
       </c>
-      <c r="J87" s="1" t="s">
+      <c r="J87" t="s">
         <v>173</v>
       </c>
-      <c r="K87" s="1" t="s">
+      <c r="K87" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4091,10 +4097,10 @@
       <c r="I88">
         <v>999</v>
       </c>
-      <c r="J88" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="K88" s="1" t="s">
+      <c r="J88" t="s">
+        <v>185</v>
+      </c>
+      <c r="K88" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4123,10 +4129,10 @@
       <c r="H89" t="s">
         <v>14</v>
       </c>
-      <c r="J89" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="K89" s="1" t="s">
+      <c r="J89" t="s">
+        <v>185</v>
+      </c>
+      <c r="K89" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4158,10 +4164,10 @@
       <c r="I90">
         <v>100000</v>
       </c>
-      <c r="J90" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="K90" s="1" t="s">
+      <c r="J90" t="s">
+        <v>188</v>
+      </c>
+      <c r="K90" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4193,10 +4199,10 @@
       <c r="I91">
         <v>100000</v>
       </c>
-      <c r="J91" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="K91" s="1" t="s">
+      <c r="J91" t="s">
+        <v>188</v>
+      </c>
+      <c r="K91" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4228,10 +4234,10 @@
       <c r="I92">
         <v>100000</v>
       </c>
-      <c r="J92" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="K92" s="1" t="s">
+      <c r="J92" t="s">
+        <v>188</v>
+      </c>
+      <c r="K92" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4263,10 +4269,10 @@
       <c r="I93">
         <v>100000</v>
       </c>
-      <c r="J93" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="K93" s="1" t="s">
+      <c r="J93" t="s">
+        <v>188</v>
+      </c>
+      <c r="K93" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4298,10 +4304,10 @@
       <c r="I94">
         <v>100000</v>
       </c>
-      <c r="J94" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="K94" s="1" t="s">
+      <c r="J94" t="s">
+        <v>188</v>
+      </c>
+      <c r="K94" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4333,10 +4339,10 @@
       <c r="I95">
         <v>100000</v>
       </c>
-      <c r="J95" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="K95" s="1" t="s">
+      <c r="J95" t="s">
+        <v>188</v>
+      </c>
+      <c r="K95" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4368,10 +4374,10 @@
       <c r="I96">
         <v>100000</v>
       </c>
-      <c r="J96" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="K96" s="1" t="s">
+      <c r="J96" t="s">
+        <v>188</v>
+      </c>
+      <c r="K96" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4403,10 +4409,10 @@
       <c r="I97">
         <v>100000</v>
       </c>
-      <c r="J97" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="K97" s="1" t="s">
+      <c r="J97" t="s">
+        <v>188</v>
+      </c>
+      <c r="K97" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4438,10 +4444,10 @@
       <c r="I98">
         <v>100000</v>
       </c>
-      <c r="J98" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="K98" s="1" t="s">
+      <c r="J98" t="s">
+        <v>188</v>
+      </c>
+      <c r="K98" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4473,10 +4479,10 @@
       <c r="I99">
         <v>1000</v>
       </c>
-      <c r="J99" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="K99" s="1" t="s">
+      <c r="J99" t="s">
+        <v>189</v>
+      </c>
+      <c r="K99" t="s">
         <v>182</v>
       </c>
     </row>
@@ -4508,10 +4514,10 @@
       <c r="I100">
         <v>1000</v>
       </c>
-      <c r="J100" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="K100" s="1" t="s">
+      <c r="J100" t="s">
+        <v>189</v>
+      </c>
+      <c r="K100" t="s">
         <v>182</v>
       </c>
     </row>
@@ -4543,10 +4549,10 @@
       <c r="I101">
         <v>1000</v>
       </c>
-      <c r="J101" s="1" t="s">
+      <c r="J101" t="s">
         <v>184</v>
       </c>
-      <c r="K101" s="1" t="s">
+      <c r="K101" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4578,10 +4584,10 @@
       <c r="I102">
         <v>1000</v>
       </c>
-      <c r="J102" s="1" t="s">
+      <c r="J102" t="s">
         <v>184</v>
       </c>
-      <c r="K102" s="1" t="s">
+      <c r="K102" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4613,10 +4619,10 @@
       <c r="I103">
         <v>1000</v>
       </c>
-      <c r="J103" s="1" t="s">
+      <c r="J103" t="s">
         <v>184</v>
       </c>
-      <c r="K103" s="1" t="s">
+      <c r="K103" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4648,10 +4654,10 @@
       <c r="I104">
         <v>1000</v>
       </c>
-      <c r="J104" s="1" t="s">
+      <c r="J104" t="s">
         <v>184</v>
       </c>
-      <c r="K104" s="1" t="s">
+      <c r="K104" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4683,10 +4689,10 @@
       <c r="I105">
         <v>1000</v>
       </c>
-      <c r="J105" s="1" t="s">
+      <c r="J105" t="s">
         <v>184</v>
       </c>
-      <c r="K105" s="1" t="s">
+      <c r="K105" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4718,10 +4724,10 @@
       <c r="I106">
         <v>1000</v>
       </c>
-      <c r="J106" s="1" t="s">
+      <c r="J106" t="s">
         <v>184</v>
       </c>
-      <c r="K106" s="1" t="s">
+      <c r="K106" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4753,10 +4759,10 @@
       <c r="I107">
         <v>1000</v>
       </c>
-      <c r="J107" s="1" t="s">
+      <c r="J107" t="s">
         <v>184</v>
       </c>
-      <c r="K107" s="1" t="s">
+      <c r="K107" t="s">
         <v>172</v>
       </c>
     </row>
@@ -5034,6 +5040,8 @@
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="86b5f7f7-2f15-447a-b5f6-1e4312ec3a6d"/>
+    <ds:schemaRef ds:uri="385505e6-e5d7-4f1a-b335-045f4e6272b3"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5047,7 +5055,22 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4B3C786-625C-47FA-923F-89919023EE24}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4B3C786-625C-47FA-923F-89919023EE24}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="385505e6-e5d7-4f1a-b335-045f4e6272b3"/>
+    <ds:schemaRef ds:uri="86b5f7f7-2f15-447a-b5f6-1e4312ec3a6d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>

--- a/controles/attribuutkenmerkwijzigingen.xlsx
+++ b/controles/attribuutkenmerkwijzigingen.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtinggeonovum.sharepoint.com/sites/msteams_fad46a/Gedeelde documenten/General/4 Werkdossier/Wijzigingsvoorstellen/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{D7F3AB6F-7286-45DD-B066-1C23A22D7238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7434B8DA-54BB-4F66-B81D-3E4538446477}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{E48346FB-E3A9-404B-B135-A733F47D585C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C3FDE83-419D-4438-81FA-0C81660EDD9B}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D12776E7-BC12-4242-A1C7-07D171B3E3CA}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="189">
   <si>
     <t>klasse</t>
   </si>
@@ -167,9 +167,6 @@
     <t>basisgeluidemissiewaarde</t>
   </si>
   <si>
-    <t>Toegestane waarde: van 0,0 tot en met 999,9</t>
-  </si>
-  <si>
     <t>Bodemvlak</t>
   </si>
   <si>
@@ -350,9 +347,6 @@
     <t>plafondcorrectie</t>
   </si>
   <si>
-    <t>-9.9</t>
-  </si>
-  <si>
     <t>SpoorstaafruwheidWaarde</t>
   </si>
   <si>
@@ -572,39 +566,9 @@
     <t>patroon toevoegen</t>
   </si>
   <si>
-    <t>maxwaarde wordt 999.99</t>
-  </si>
-  <si>
-    <t>Ja</t>
-  </si>
-  <si>
-    <t>maxwaarde wordt 999.9</t>
-  </si>
-  <si>
-    <t>streepje uit patroon</t>
-  </si>
-  <si>
     <t>min en max verwijderen</t>
   </si>
   <si>
-    <t>maxwaarde wordt 99.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patroon aanpassen </t>
-  </si>
-  <si>
-    <t>maxwaarde wordt 199.9</t>
-  </si>
-  <si>
-    <t>ja</t>
-  </si>
-  <si>
-    <t>patroon toevoegen en maxwaarde wordt 999.99</t>
-  </si>
-  <si>
-    <t>meeteenheid km/u</t>
-  </si>
-  <si>
     <t>geen</t>
   </si>
   <si>
@@ -614,23 +578,59 @@
     <t>meeteenheid fractie</t>
   </si>
   <si>
-    <t>meeteenheid aantal</t>
-  </si>
-  <si>
-    <t>meeteenheid km/u en min -&gt; 0, max -&gt;999</t>
-  </si>
-  <si>
-    <t>maxwaarde wordt 99.9 (ook in patroon)</t>
+    <t>aangepast</t>
+  </si>
+  <si>
+    <t>999.99</t>
+  </si>
+  <si>
+    <t>niet nodig</t>
+  </si>
+  <si>
+    <t>199.9</t>
+  </si>
+  <si>
+    <t>Toegestane waarde: van 0,0 tot en met 199,9</t>
+  </si>
+  <si>
+    <t>"-"uit patroon en meeteenheid: fractie</t>
+  </si>
+  <si>
+    <t>9.9</t>
+  </si>
+  <si>
+    <t>99.9</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>Toegestane waarde: van -199,9 tot en met 199,9 en 1 cijfers na de komma.</t>
+  </si>
+  <si>
+    <t>999.9</t>
+  </si>
+  <si>
+    <t>meeteenheid km/u en patroon max -&gt; 1000</t>
+  </si>
+  <si>
+    <t>meeteenheid aantal per uur</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -656,13 +656,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -706,14 +710,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{E58A355E-256C-4D1C-8C5E-3A973B36854D}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="12" unboundColumnsRight="2">
-    <queryTableFields count="11">
+  <queryTableRefresh nextId="13" unboundColumnsRight="3">
+    <queryTableFields count="12">
       <queryTableField id="1" name="klasse" tableColumnId="1"/>
       <queryTableField id="2" name="attribuut" tableColumnId="2"/>
       <queryTableField id="3" name="type" tableColumnId="3"/>
@@ -725,26 +725,28 @@
       <queryTableField id="9" name="max" tableColumnId="9"/>
       <queryTableField id="10" dataBound="0" tableColumnId="10"/>
       <queryTableField id="11" dataBound="0" tableColumnId="11"/>
+      <queryTableField id="12" dataBound="0" tableColumnId="12"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FBE24DF2-D59E-47AD-94A6-14FCB327D3D3}" name="mimreport" displayName="mimreport" ref="A1:K107" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:K107" xr:uid="{FBE24DF2-D59E-47AD-94A6-14FCB327D3D3}"/>
-  <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{6A58B7F8-88AF-45D7-9EE8-C5173BEAF39C}" uniqueName="1" name="klasse" queryTableFieldId="1" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{A475521D-8229-4DA6-945B-2E4BDE9038CB}" uniqueName="2" name="attribuut" queryTableFieldId="2" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{D1A060EB-ED7D-48D0-8305-910A0E49ACA6}" uniqueName="3" name="type" queryTableFieldId="3" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{2547E5B6-CDD7-4278-8FEA-9C1870482E4B}" uniqueName="4" name="kard" queryTableFieldId="4" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{1B047BF0-7C89-47AB-A790-E2E32A995AAD}" uniqueName="5" name="lengte" queryTableFieldId="5" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{EA1F6914-7928-4F37-9FB5-080744A93E8D}" uniqueName="6" name="patroon" queryTableFieldId="6" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{F9E055E8-7C2D-4BD0-8080-2535E903DF97}" uniqueName="7" name="meeteenheid" queryTableFieldId="7" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{A73D5F8D-FD46-474A-8126-8462CF1C19C9}" uniqueName="8" name="min" queryTableFieldId="8" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FBE24DF2-D59E-47AD-94A6-14FCB327D3D3}" name="mimreport" displayName="mimreport" ref="A1:L107" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:L107" xr:uid="{FBE24DF2-D59E-47AD-94A6-14FCB327D3D3}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{6A58B7F8-88AF-45D7-9EE8-C5173BEAF39C}" uniqueName="1" name="klasse" queryTableFieldId="1" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{A475521D-8229-4DA6-945B-2E4BDE9038CB}" uniqueName="2" name="attribuut" queryTableFieldId="2" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{D1A060EB-ED7D-48D0-8305-910A0E49ACA6}" uniqueName="3" name="type" queryTableFieldId="3" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{2547E5B6-CDD7-4278-8FEA-9C1870482E4B}" uniqueName="4" name="kard" queryTableFieldId="4" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{1B047BF0-7C89-47AB-A790-E2E32A995AAD}" uniqueName="5" name="lengte" queryTableFieldId="5" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{EA1F6914-7928-4F37-9FB5-080744A93E8D}" uniqueName="6" name="patroon" queryTableFieldId="6" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{F9E055E8-7C2D-4BD0-8080-2535E903DF97}" uniqueName="7" name="meeteenheid" queryTableFieldId="7" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{A73D5F8D-FD46-474A-8126-8462CF1C19C9}" uniqueName="8" name="min" queryTableFieldId="8" dataDxfId="3"/>
     <tableColumn id="9" xr3:uid="{31F03B7E-2A74-4446-8D37-D6ACC510F62A}" uniqueName="9" name="max" queryTableFieldId="9"/>
-    <tableColumn id="10" xr3:uid="{2422F590-BC6B-483D-B45F-ABC6B5C4B109}" uniqueName="10" name="verandering" queryTableFieldId="10" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{00DF0C2B-2027-4BE7-BD2F-5AF303BE27D8}" uniqueName="11" name="xsd wijzigt" queryTableFieldId="11" dataDxfId="0"/>
+    <tableColumn id="10" xr3:uid="{2422F590-BC6B-483D-B45F-ABC6B5C4B109}" uniqueName="10" name="verandering" queryTableFieldId="10" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{00DF0C2B-2027-4BE7-BD2F-5AF303BE27D8}" uniqueName="11" name="xsd wijzigt" queryTableFieldId="11" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{CB825BD9-165F-4898-94FF-F79CCC94A249}" uniqueName="12" name="aangepast" queryTableFieldId="12" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1047,23 +1049,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09AA787F-8677-4228-918C-9EA7766DB8D7}">
-  <dimension ref="A1:K107"/>
+  <dimension ref="A1:L107"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="48.77734375" customWidth="1"/>
-    <col min="3" max="3" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.6640625" customWidth="1"/>
+    <col min="3" max="3" width="20.44140625" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="80.33203125" customWidth="1"/>
-    <col min="7" max="7" width="8.77734375" customWidth="1"/>
-    <col min="8" max="8" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="76.21875" customWidth="1"/>
+    <col min="7" max="7" width="17.6640625" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
     <col min="9" max="9" width="11.5546875" customWidth="1"/>
-    <col min="10" max="10" width="38.77734375" customWidth="1"/>
+    <col min="10" max="10" width="37.21875" customWidth="1"/>
     <col min="11" max="11" width="14.44140625" customWidth="1"/>
+    <col min="12" max="12" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1092,13 +1095,16 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+      <c r="L1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1127,13 +1133,16 @@
         <v>999</v>
       </c>
       <c r="J2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L2">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1162,13 +1171,16 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="K3" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1197,13 +1209,16 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="K4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L4">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1232,13 +1247,16 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="K5" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L5">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -1267,13 +1285,16 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="K6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L6">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -1302,13 +1323,16 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="K7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L7">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1337,13 +1361,16 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="K8" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L8">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1372,13 +1399,16 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="K9" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L9">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1407,13 +1437,16 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="K10" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L10">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -1442,13 +1475,16 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="K11" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L11">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -1477,13 +1513,16 @@
         <v>360</v>
       </c>
       <c r="J12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K12" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L12">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1512,13 +1551,16 @@
         <v>360</v>
       </c>
       <c r="J13" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K13" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L13">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -1543,17 +1585,20 @@
       <c r="H14" t="s">
         <v>36</v>
       </c>
-      <c r="I14">
-        <v>99999</v>
+      <c r="I14" t="s">
+        <v>177</v>
       </c>
       <c r="J14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K14" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L14" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -1578,17 +1623,20 @@
       <c r="H15" t="s">
         <v>36</v>
       </c>
-      <c r="I15">
-        <v>99999</v>
+      <c r="I15" t="s">
+        <v>177</v>
       </c>
       <c r="J15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K15" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L15" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>34</v>
       </c>
@@ -1613,17 +1661,20 @@
       <c r="H16" t="s">
         <v>36</v>
       </c>
-      <c r="I16">
-        <v>99999</v>
+      <c r="I16" t="s">
+        <v>177</v>
       </c>
       <c r="J16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K16" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L16" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -1648,17 +1699,20 @@
       <c r="H17" t="s">
         <v>36</v>
       </c>
-      <c r="I17">
-        <v>99999</v>
+      <c r="I17" t="s">
+        <v>177</v>
       </c>
       <c r="J17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K17" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L17" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -1683,17 +1737,20 @@
       <c r="H18" t="s">
         <v>36</v>
       </c>
-      <c r="I18">
-        <v>99999</v>
+      <c r="I18" t="s">
+        <v>177</v>
       </c>
       <c r="J18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K18" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L18" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -1718,17 +1775,20 @@
       <c r="H19" t="s">
         <v>36</v>
       </c>
-      <c r="I19">
-        <v>99999</v>
+      <c r="I19" t="s">
+        <v>177</v>
       </c>
       <c r="J19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K19" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L19" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -1753,17 +1813,20 @@
       <c r="H20" t="s">
         <v>36</v>
       </c>
-      <c r="I20">
-        <v>99999</v>
+      <c r="I20" t="s">
+        <v>177</v>
       </c>
       <c r="J20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K20" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L20" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -1788,17 +1851,20 @@
       <c r="H21" t="s">
         <v>36</v>
       </c>
-      <c r="I21">
-        <v>99999</v>
+      <c r="I21" t="s">
+        <v>177</v>
       </c>
       <c r="J21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K21" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L21" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -1823,17 +1889,20 @@
       <c r="H22" t="s">
         <v>36</v>
       </c>
-      <c r="I22">
-        <v>99999</v>
+      <c r="I22" t="s">
+        <v>177</v>
       </c>
       <c r="J22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K22" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L22" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -1850,7 +1919,7 @@
         <v>13</v>
       </c>
       <c r="F23" t="s">
-        <v>39</v>
+        <v>180</v>
       </c>
       <c r="G23" t="s">
         <v>15</v>
@@ -1858,22 +1927,25 @@
       <c r="H23" t="s">
         <v>16</v>
       </c>
-      <c r="I23">
-        <v>1999</v>
+      <c r="I23" t="s">
+        <v>179</v>
       </c>
       <c r="J23" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="K23" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L23" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" t="s">
         <v>40</v>
-      </c>
-      <c r="B24" t="s">
-        <v>41</v>
       </c>
       <c r="C24" t="s">
         <v>11</v>
@@ -1885,7 +1957,7 @@
         <v>13</v>
       </c>
       <c r="F24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G24" t="s">
         <v>14</v>
@@ -1897,18 +1969,21 @@
         <v>1</v>
       </c>
       <c r="J24" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="K24" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L24">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" t="s">
         <v>43</v>
-      </c>
-      <c r="B25" t="s">
-        <v>44</v>
       </c>
       <c r="C25" t="s">
         <v>17</v>
@@ -1920,30 +1995,33 @@
         <v>14</v>
       </c>
       <c r="F25" t="s">
+        <v>44</v>
+      </c>
+      <c r="G25" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" t="s">
+        <v>14</v>
+      </c>
+      <c r="J25" t="s">
+        <v>169</v>
+      </c>
+      <c r="K25" t="s">
+        <v>170</v>
+      </c>
+      <c r="L25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" t="s">
         <v>45</v>
       </c>
-      <c r="G25" t="s">
-        <v>14</v>
-      </c>
-      <c r="H25" t="s">
-        <v>14</v>
-      </c>
-      <c r="J25" t="s">
-        <v>171</v>
-      </c>
-      <c r="K25" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>46</v>
-      </c>
-      <c r="C26" t="s">
-        <v>47</v>
       </c>
       <c r="D26" t="s">
         <v>12</v>
@@ -1961,21 +2039,24 @@
         <v>14</v>
       </c>
       <c r="J26" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="K26" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L26">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B27" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" t="s">
         <v>48</v>
-      </c>
-      <c r="C27" t="s">
-        <v>49</v>
       </c>
       <c r="D27" t="s">
         <v>12</v>
@@ -1996,50 +2077,56 @@
         <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="K27" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L27">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" t="s">
         <v>50</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" t="s">
+        <v>14</v>
+      </c>
+      <c r="J28" t="s">
+        <v>173</v>
+      </c>
+      <c r="K28" t="s">
+        <v>170</v>
+      </c>
+      <c r="L28">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>51</v>
       </c>
-      <c r="C28" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28" t="s">
-        <v>12</v>
-      </c>
-      <c r="E28" t="s">
-        <v>14</v>
-      </c>
-      <c r="F28" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28" t="s">
-        <v>14</v>
-      </c>
-      <c r="H28" t="s">
-        <v>14</v>
-      </c>
-      <c r="J28" t="s">
-        <v>185</v>
-      </c>
-      <c r="K28" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="B29" t="s">
         <v>52</v>
-      </c>
-      <c r="B29" t="s">
-        <v>53</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
@@ -2054,59 +2141,65 @@
         <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
       </c>
-      <c r="I29">
-        <v>99</v>
+      <c r="I29" t="s">
+        <v>182</v>
       </c>
       <c r="J29" t="s">
+        <v>171</v>
+      </c>
+      <c r="K29" t="s">
+        <v>170</v>
+      </c>
+      <c r="L29">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" t="s">
+        <v>48</v>
+      </c>
+      <c r="D30" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" t="s">
+        <v>14</v>
+      </c>
+      <c r="F30" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" t="s">
+        <v>14</v>
+      </c>
+      <c r="J30" t="s">
         <v>173</v>
       </c>
-      <c r="K29" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>52</v>
-      </c>
-      <c r="B30" t="s">
+      <c r="K30" t="s">
+        <v>170</v>
+      </c>
+      <c r="L30">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>55</v>
       </c>
-      <c r="C30" t="s">
-        <v>49</v>
-      </c>
-      <c r="D30" t="s">
-        <v>12</v>
-      </c>
-      <c r="E30" t="s">
-        <v>14</v>
-      </c>
-      <c r="F30" t="s">
-        <v>14</v>
-      </c>
-      <c r="G30" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" t="s">
-        <v>14</v>
-      </c>
-      <c r="J30" t="s">
-        <v>185</v>
-      </c>
-      <c r="K30" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="B31" t="s">
         <v>56</v>
-      </c>
-      <c r="B31" t="s">
-        <v>57</v>
       </c>
       <c r="C31" t="s">
         <v>11</v>
@@ -2121,24 +2214,27 @@
         <v>14</v>
       </c>
       <c r="G31" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H31" t="s">
         <v>16</v>
       </c>
       <c r="J31" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K31" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L31">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>57</v>
+      </c>
+      <c r="B32" t="s">
         <v>58</v>
-      </c>
-      <c r="B32" t="s">
-        <v>59</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
@@ -2153,30 +2249,33 @@
         <v>14</v>
       </c>
       <c r="G32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I32">
         <v>1000</v>
       </c>
       <c r="J32" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K32" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L32">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D33" t="s">
         <v>19</v>
@@ -2191,27 +2290,30 @@
         <v>14</v>
       </c>
       <c r="H33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I33">
         <v>1</v>
       </c>
       <c r="J33" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="K33" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L33">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D34" t="s">
         <v>19</v>
@@ -2232,21 +2334,24 @@
         <v>1</v>
       </c>
       <c r="J34" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="K34" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L34">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D35" t="s">
         <v>19</v>
@@ -2267,30 +2372,33 @@
         <v>1</v>
       </c>
       <c r="J35" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="K35" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L35">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>64</v>
+      </c>
+      <c r="B36" t="s">
         <v>65</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" t="s">
         <v>66</v>
       </c>
-      <c r="C36" t="s">
-        <v>11</v>
-      </c>
-      <c r="D36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>67</v>
-      </c>
-      <c r="F36" t="s">
-        <v>68</v>
       </c>
       <c r="G36" t="s">
         <v>15</v>
@@ -2302,18 +2410,21 @@
         <v>99</v>
       </c>
       <c r="J36" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="K36" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L36" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" t="s">
         <v>69</v>
-      </c>
-      <c r="B37" t="s">
-        <v>70</v>
       </c>
       <c r="C37" t="s">
         <v>11</v>
@@ -2328,27 +2439,30 @@
         <v>14</v>
       </c>
       <c r="G37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H37" t="s">
+        <v>70</v>
+      </c>
+      <c r="I37" t="s">
+        <v>184</v>
+      </c>
+      <c r="J37" t="s">
+        <v>171</v>
+      </c>
+      <c r="K37" t="s">
+        <v>170</v>
+      </c>
+      <c r="L37">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>68</v>
+      </c>
+      <c r="B38" t="s">
         <v>71</v>
-      </c>
-      <c r="I37">
-        <v>45</v>
-      </c>
-      <c r="J37" t="s">
-        <v>173</v>
-      </c>
-      <c r="K37" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>69</v>
-      </c>
-      <c r="B38" t="s">
-        <v>72</v>
       </c>
       <c r="C38" t="s">
         <v>11</v>
@@ -2368,22 +2482,25 @@
       <c r="H38" t="s">
         <v>16</v>
       </c>
-      <c r="I38">
-        <v>999</v>
+      <c r="I38" t="s">
+        <v>183</v>
       </c>
       <c r="J38" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K38" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L38">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B39" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C39" t="s">
         <v>11</v>
@@ -2403,54 +2520,60 @@
       <c r="H39" t="s">
         <v>16</v>
       </c>
-      <c r="I39">
-        <v>999</v>
+      <c r="I39" t="s">
+        <v>183</v>
       </c>
       <c r="J39" t="s">
+        <v>171</v>
+      </c>
+      <c r="K39" t="s">
+        <v>170</v>
+      </c>
+      <c r="L39">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>68</v>
+      </c>
+      <c r="B40" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" t="s">
+        <v>48</v>
+      </c>
+      <c r="D40" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40" t="s">
+        <v>14</v>
+      </c>
+      <c r="F40" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40" t="s">
+        <v>14</v>
+      </c>
+      <c r="H40" t="s">
+        <v>14</v>
+      </c>
+      <c r="J40" t="s">
         <v>173</v>
       </c>
-      <c r="K39" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>69</v>
-      </c>
-      <c r="B40" t="s">
+      <c r="K40" t="s">
+        <v>170</v>
+      </c>
+      <c r="L40" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>74</v>
       </c>
-      <c r="C40" t="s">
-        <v>49</v>
-      </c>
-      <c r="D40" t="s">
-        <v>12</v>
-      </c>
-      <c r="E40" t="s">
-        <v>14</v>
-      </c>
-      <c r="F40" t="s">
-        <v>14</v>
-      </c>
-      <c r="G40" t="s">
-        <v>14</v>
-      </c>
-      <c r="H40" t="s">
-        <v>14</v>
-      </c>
-      <c r="J40" t="s">
-        <v>185</v>
-      </c>
-      <c r="K40" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+      <c r="B41" t="s">
         <v>75</v>
-      </c>
-      <c r="B41" t="s">
-        <v>76</v>
       </c>
       <c r="C41" t="s">
         <v>11</v>
@@ -2462,7 +2585,7 @@
         <v>13</v>
       </c>
       <c r="F41" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G41" t="s">
         <v>15</v>
@@ -2470,22 +2593,25 @@
       <c r="H41" t="s">
         <v>16</v>
       </c>
-      <c r="I41">
-        <v>999</v>
+      <c r="I41" t="s">
+        <v>183</v>
       </c>
       <c r="J41" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="K41" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L41" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B42" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C42" t="s">
         <v>11</v>
@@ -2505,22 +2631,25 @@
       <c r="H42" t="s">
         <v>16</v>
       </c>
-      <c r="I42">
-        <v>999</v>
+      <c r="I42" t="s">
+        <v>183</v>
       </c>
       <c r="J42" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K42" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L42">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>78</v>
+      </c>
+      <c r="B43" t="s">
         <v>79</v>
-      </c>
-      <c r="B43" t="s">
-        <v>80</v>
       </c>
       <c r="C43" t="s">
         <v>11</v>
@@ -2532,62 +2661,68 @@
         <v>13</v>
       </c>
       <c r="F43" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G43" t="s">
         <v>32</v>
       </c>
       <c r="H43" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I43">
         <v>45</v>
       </c>
       <c r="J43" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="K43" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L43" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>78</v>
+      </c>
+      <c r="B44" t="s">
+        <v>54</v>
+      </c>
+      <c r="C44" t="s">
+        <v>48</v>
+      </c>
+      <c r="D44" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" t="s">
+        <v>14</v>
+      </c>
+      <c r="F44" t="s">
+        <v>14</v>
+      </c>
+      <c r="G44" t="s">
+        <v>14</v>
+      </c>
+      <c r="H44" t="s">
+        <v>14</v>
+      </c>
+      <c r="J44" t="s">
+        <v>173</v>
+      </c>
+      <c r="K44" t="s">
+        <v>170</v>
+      </c>
+      <c r="L44" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>82</v>
+      </c>
+      <c r="B45" t="s">
         <v>79</v>
-      </c>
-      <c r="B44" t="s">
-        <v>55</v>
-      </c>
-      <c r="C44" t="s">
-        <v>49</v>
-      </c>
-      <c r="D44" t="s">
-        <v>12</v>
-      </c>
-      <c r="E44" t="s">
-        <v>14</v>
-      </c>
-      <c r="F44" t="s">
-        <v>14</v>
-      </c>
-      <c r="G44" t="s">
-        <v>14</v>
-      </c>
-      <c r="H44" t="s">
-        <v>14</v>
-      </c>
-      <c r="J44" t="s">
-        <v>185</v>
-      </c>
-      <c r="K44" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>83</v>
-      </c>
-      <c r="B45" t="s">
-        <v>80</v>
       </c>
       <c r="C45" t="s">
         <v>11</v>
@@ -2599,62 +2734,68 @@
         <v>13</v>
       </c>
       <c r="F45" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s">
         <v>32</v>
       </c>
       <c r="H45" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I45">
         <v>45</v>
       </c>
       <c r="J45" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="K45" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L45" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>82</v>
+      </c>
+      <c r="B46" t="s">
+        <v>54</v>
+      </c>
+      <c r="C46" t="s">
+        <v>48</v>
+      </c>
+      <c r="D46" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46" t="s">
+        <v>14</v>
+      </c>
+      <c r="F46" t="s">
+        <v>14</v>
+      </c>
+      <c r="G46" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" t="s">
+        <v>14</v>
+      </c>
+      <c r="J46" t="s">
+        <v>173</v>
+      </c>
+      <c r="K46" t="s">
+        <v>170</v>
+      </c>
+      <c r="L46" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>83</v>
       </c>
-      <c r="B46" t="s">
-        <v>55</v>
-      </c>
-      <c r="C46" t="s">
-        <v>49</v>
-      </c>
-      <c r="D46" t="s">
-        <v>12</v>
-      </c>
-      <c r="E46" t="s">
-        <v>14</v>
-      </c>
-      <c r="F46" t="s">
-        <v>14</v>
-      </c>
-      <c r="G46" t="s">
-        <v>14</v>
-      </c>
-      <c r="H46" t="s">
-        <v>14</v>
-      </c>
-      <c r="J46" t="s">
-        <v>185</v>
-      </c>
-      <c r="K46" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="B47" t="s">
         <v>84</v>
-      </c>
-      <c r="B47" t="s">
-        <v>85</v>
       </c>
       <c r="C47" t="s">
         <v>11</v>
@@ -2666,7 +2807,7 @@
         <v>13</v>
       </c>
       <c r="F47" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G47" t="s">
         <v>14</v>
@@ -2678,18 +2819,21 @@
         <v>1</v>
       </c>
       <c r="J47" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="K47" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L47">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>86</v>
+      </c>
+      <c r="B48" t="s">
         <v>87</v>
-      </c>
-      <c r="B48" t="s">
-        <v>88</v>
       </c>
       <c r="C48" t="s">
         <v>11</v>
@@ -2701,30 +2845,33 @@
         <v>13</v>
       </c>
       <c r="F48" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G48" t="s">
         <v>15</v>
       </c>
       <c r="H48" t="s">
+        <v>89</v>
+      </c>
+      <c r="I48" t="s">
+        <v>179</v>
+      </c>
+      <c r="J48" t="s">
+        <v>173</v>
+      </c>
+      <c r="K48" t="s">
+        <v>170</v>
+      </c>
+      <c r="L48" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>90</v>
       </c>
-      <c r="I48">
-        <v>1999</v>
-      </c>
-      <c r="J48" t="s">
-        <v>181</v>
-      </c>
-      <c r="K48" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="B49" t="s">
         <v>91</v>
-      </c>
-      <c r="B49" t="s">
-        <v>92</v>
       </c>
       <c r="C49" t="s">
         <v>11</v>
@@ -2736,7 +2883,7 @@
         <v>13</v>
       </c>
       <c r="F49" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G49" t="s">
         <v>15</v>
@@ -2744,22 +2891,25 @@
       <c r="H49" t="s">
         <v>16</v>
       </c>
-      <c r="I49">
-        <v>999</v>
+      <c r="I49" t="s">
+        <v>183</v>
       </c>
       <c r="J49" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="K49" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L49" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>93</v>
+      </c>
+      <c r="B50" t="s">
         <v>94</v>
-      </c>
-      <c r="B50" t="s">
-        <v>95</v>
       </c>
       <c r="C50" t="s">
         <v>11</v>
@@ -2779,54 +2929,60 @@
       <c r="H50" t="s">
         <v>16</v>
       </c>
-      <c r="I50">
-        <v>99999</v>
+      <c r="I50" t="s">
+        <v>177</v>
       </c>
       <c r="J50" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="K50" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L50">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>95</v>
+      </c>
+      <c r="B51" t="s">
         <v>96</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
+        <v>48</v>
+      </c>
+      <c r="D51" t="s">
+        <v>12</v>
+      </c>
+      <c r="E51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F51" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" t="s">
+        <v>14</v>
+      </c>
+      <c r="H51" t="s">
+        <v>14</v>
+      </c>
+      <c r="J51" t="s">
+        <v>173</v>
+      </c>
+      <c r="K51" t="s">
+        <v>170</v>
+      </c>
+      <c r="L51" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>97</v>
       </c>
-      <c r="C51" t="s">
-        <v>49</v>
-      </c>
-      <c r="D51" t="s">
-        <v>12</v>
-      </c>
-      <c r="E51" t="s">
-        <v>14</v>
-      </c>
-      <c r="F51" t="s">
-        <v>14</v>
-      </c>
-      <c r="G51" t="s">
-        <v>14</v>
-      </c>
-      <c r="H51" t="s">
-        <v>14</v>
-      </c>
-      <c r="J51" t="s">
-        <v>185</v>
-      </c>
-      <c r="K51" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="B52" t="s">
         <v>98</v>
-      </c>
-      <c r="B52" t="s">
-        <v>99</v>
       </c>
       <c r="C52" t="s">
         <v>11</v>
@@ -2838,30 +2994,36 @@
         <v>13</v>
       </c>
       <c r="F52" t="s">
-        <v>14</v>
+        <v>185</v>
       </c>
       <c r="G52" t="s">
         <v>15</v>
       </c>
-      <c r="H52" t="s">
-        <v>100</v>
+      <c r="H52" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I52" t="s">
+        <v>179</v>
       </c>
       <c r="J52" t="s">
         <v>173</v>
       </c>
       <c r="K52" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L52">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B53" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C53" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D53" t="s">
         <v>12</v>
@@ -2879,18 +3041,21 @@
         <v>14</v>
       </c>
       <c r="J53" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="K53" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L53" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B54" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C54" t="s">
         <v>11</v>
@@ -2901,31 +3066,31 @@
       <c r="E54" t="s">
         <v>13</v>
       </c>
-      <c r="F54" t="s">
-        <v>14</v>
-      </c>
       <c r="G54" t="s">
+        <v>101</v>
+      </c>
+      <c r="H54" t="s">
+        <v>102</v>
+      </c>
+      <c r="I54" t="s">
+        <v>183</v>
+      </c>
+      <c r="J54" t="s">
+        <v>171</v>
+      </c>
+      <c r="K54" t="s">
+        <v>170</v>
+      </c>
+      <c r="L54">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>99</v>
+      </c>
+      <c r="B55" t="s">
         <v>103</v>
-      </c>
-      <c r="H54" t="s">
-        <v>104</v>
-      </c>
-      <c r="I54">
-        <v>999</v>
-      </c>
-      <c r="J54" t="s">
-        <v>173</v>
-      </c>
-      <c r="K54" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>101</v>
-      </c>
-      <c r="B55" t="s">
-        <v>105</v>
       </c>
       <c r="C55" t="s">
         <v>11</v>
@@ -2940,27 +3105,30 @@
         <v>14</v>
       </c>
       <c r="G55" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H55" t="s">
+        <v>102</v>
+      </c>
+      <c r="I55" t="s">
+        <v>183</v>
+      </c>
+      <c r="J55" t="s">
+        <v>171</v>
+      </c>
+      <c r="K55" t="s">
+        <v>170</v>
+      </c>
+      <c r="L55">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>99</v>
+      </c>
+      <c r="B56" t="s">
         <v>104</v>
-      </c>
-      <c r="I55">
-        <v>999</v>
-      </c>
-      <c r="J55" t="s">
-        <v>173</v>
-      </c>
-      <c r="K55" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>101</v>
-      </c>
-      <c r="B56" t="s">
-        <v>106</v>
       </c>
       <c r="C56" t="s">
         <v>11</v>
@@ -2975,27 +3143,30 @@
         <v>14</v>
       </c>
       <c r="G56" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H56" t="s">
-        <v>104</v>
-      </c>
-      <c r="I56">
-        <v>999</v>
+        <v>102</v>
+      </c>
+      <c r="I56" t="s">
+        <v>183</v>
       </c>
       <c r="J56" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K56" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L56">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B57" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C57" t="s">
         <v>11</v>
@@ -3010,27 +3181,30 @@
         <v>14</v>
       </c>
       <c r="G57" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H57" t="s">
-        <v>104</v>
-      </c>
-      <c r="I57">
-        <v>999</v>
+        <v>102</v>
+      </c>
+      <c r="I57" t="s">
+        <v>183</v>
       </c>
       <c r="J57" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K57" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L57">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B58" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C58" t="s">
         <v>11</v>
@@ -3045,27 +3219,30 @@
         <v>14</v>
       </c>
       <c r="G58" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H58" t="s">
-        <v>104</v>
-      </c>
-      <c r="I58">
-        <v>999</v>
+        <v>102</v>
+      </c>
+      <c r="I58" t="s">
+        <v>183</v>
       </c>
       <c r="J58" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K58" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L58">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B59" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C59" t="s">
         <v>11</v>
@@ -3080,27 +3257,30 @@
         <v>14</v>
       </c>
       <c r="G59" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H59" t="s">
-        <v>104</v>
-      </c>
-      <c r="I59">
-        <v>999</v>
+        <v>102</v>
+      </c>
+      <c r="I59" t="s">
+        <v>183</v>
       </c>
       <c r="J59" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K59" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L59">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B60" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C60" t="s">
         <v>11</v>
@@ -3115,27 +3295,30 @@
         <v>14</v>
       </c>
       <c r="G60" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H60" t="s">
-        <v>104</v>
-      </c>
-      <c r="I60">
-        <v>999</v>
+        <v>102</v>
+      </c>
+      <c r="I60" t="s">
+        <v>183</v>
       </c>
       <c r="J60" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K60" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L60">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B61" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C61" t="s">
         <v>11</v>
@@ -3150,27 +3333,30 @@
         <v>14</v>
       </c>
       <c r="G61" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H61" t="s">
-        <v>104</v>
-      </c>
-      <c r="I61">
-        <v>999</v>
+        <v>102</v>
+      </c>
+      <c r="I61" t="s">
+        <v>183</v>
       </c>
       <c r="J61" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K61" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L61">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B62" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C62" t="s">
         <v>11</v>
@@ -3185,27 +3371,30 @@
         <v>14</v>
       </c>
       <c r="G62" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H62" t="s">
-        <v>104</v>
-      </c>
-      <c r="I62">
-        <v>999</v>
+        <v>102</v>
+      </c>
+      <c r="I62" t="s">
+        <v>183</v>
       </c>
       <c r="J62" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K62" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L62">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B63" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C63" t="s">
         <v>11</v>
@@ -3220,27 +3409,30 @@
         <v>14</v>
       </c>
       <c r="G63" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H63" t="s">
-        <v>104</v>
-      </c>
-      <c r="I63">
-        <v>999</v>
+        <v>102</v>
+      </c>
+      <c r="I63" t="s">
+        <v>183</v>
       </c>
       <c r="J63" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K63" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L63">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B64" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C64" t="s">
         <v>11</v>
@@ -3255,27 +3447,30 @@
         <v>14</v>
       </c>
       <c r="G64" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H64" t="s">
-        <v>104</v>
-      </c>
-      <c r="I64">
-        <v>999</v>
+        <v>102</v>
+      </c>
+      <c r="I64" t="s">
+        <v>183</v>
       </c>
       <c r="J64" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K64" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L64">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B65" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C65" t="s">
         <v>11</v>
@@ -3290,27 +3485,30 @@
         <v>14</v>
       </c>
       <c r="G65" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H65" t="s">
-        <v>104</v>
-      </c>
-      <c r="I65">
-        <v>999</v>
+        <v>102</v>
+      </c>
+      <c r="I65" t="s">
+        <v>183</v>
       </c>
       <c r="J65" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K65" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L65">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B66" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C66" t="s">
         <v>11</v>
@@ -3325,27 +3523,30 @@
         <v>14</v>
       </c>
       <c r="G66" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H66" t="s">
-        <v>104</v>
-      </c>
-      <c r="I66">
-        <v>999</v>
+        <v>102</v>
+      </c>
+      <c r="I66" t="s">
+        <v>183</v>
       </c>
       <c r="J66" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K66" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L66">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B67" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C67" t="s">
         <v>11</v>
@@ -3360,27 +3561,30 @@
         <v>14</v>
       </c>
       <c r="G67" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H67" t="s">
-        <v>104</v>
-      </c>
-      <c r="I67">
-        <v>999</v>
+        <v>102</v>
+      </c>
+      <c r="I67" t="s">
+        <v>183</v>
       </c>
       <c r="J67" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K67" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L67">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B68" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C68" t="s">
         <v>11</v>
@@ -3395,27 +3599,30 @@
         <v>14</v>
       </c>
       <c r="G68" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H68" t="s">
-        <v>104</v>
-      </c>
-      <c r="I68">
-        <v>999</v>
+        <v>102</v>
+      </c>
+      <c r="I68" t="s">
+        <v>183</v>
       </c>
       <c r="J68" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K68" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L68">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B69" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C69" t="s">
         <v>11</v>
@@ -3430,27 +3637,30 @@
         <v>14</v>
       </c>
       <c r="G69" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H69" t="s">
-        <v>104</v>
-      </c>
-      <c r="I69">
-        <v>999</v>
+        <v>102</v>
+      </c>
+      <c r="I69" t="s">
+        <v>183</v>
       </c>
       <c r="J69" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K69" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L69">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B70" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C70" t="s">
         <v>11</v>
@@ -3465,27 +3675,30 @@
         <v>14</v>
       </c>
       <c r="G70" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H70" t="s">
-        <v>104</v>
-      </c>
-      <c r="I70">
-        <v>999</v>
+        <v>102</v>
+      </c>
+      <c r="I70" t="s">
+        <v>183</v>
       </c>
       <c r="J70" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K70" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L70">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B71" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C71" t="s">
         <v>11</v>
@@ -3500,27 +3713,30 @@
         <v>14</v>
       </c>
       <c r="G71" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H71" t="s">
-        <v>104</v>
-      </c>
-      <c r="I71">
-        <v>999</v>
+        <v>102</v>
+      </c>
+      <c r="I71" t="s">
+        <v>183</v>
       </c>
       <c r="J71" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K71" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L71">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B72" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C72" t="s">
         <v>11</v>
@@ -3535,27 +3751,30 @@
         <v>14</v>
       </c>
       <c r="G72" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H72" t="s">
-        <v>104</v>
-      </c>
-      <c r="I72">
-        <v>999</v>
+        <v>102</v>
+      </c>
+      <c r="I72" t="s">
+        <v>183</v>
       </c>
       <c r="J72" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K72" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L72">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B73" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C73" t="s">
         <v>11</v>
@@ -3570,27 +3789,30 @@
         <v>14</v>
       </c>
       <c r="G73" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H73" t="s">
-        <v>104</v>
-      </c>
-      <c r="I73">
-        <v>999</v>
+        <v>102</v>
+      </c>
+      <c r="I73" t="s">
+        <v>183</v>
       </c>
       <c r="J73" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K73" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L73">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B74" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C74" t="s">
         <v>11</v>
@@ -3605,27 +3827,30 @@
         <v>14</v>
       </c>
       <c r="G74" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H74" t="s">
-        <v>104</v>
-      </c>
-      <c r="I74">
-        <v>999</v>
+        <v>102</v>
+      </c>
+      <c r="I74" t="s">
+        <v>183</v>
       </c>
       <c r="J74" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K74" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L74">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B75" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C75" t="s">
         <v>11</v>
@@ -3640,27 +3865,30 @@
         <v>14</v>
       </c>
       <c r="G75" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H75" t="s">
-        <v>104</v>
-      </c>
-      <c r="I75">
-        <v>999</v>
+        <v>102</v>
+      </c>
+      <c r="I75" t="s">
+        <v>183</v>
       </c>
       <c r="J75" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K75" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L75">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B76" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C76" t="s">
         <v>11</v>
@@ -3675,27 +3903,30 @@
         <v>14</v>
       </c>
       <c r="G76" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H76" t="s">
-        <v>104</v>
-      </c>
-      <c r="I76">
-        <v>999</v>
+        <v>102</v>
+      </c>
+      <c r="I76" t="s">
+        <v>183</v>
       </c>
       <c r="J76" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K76" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L76">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B77" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C77" t="s">
         <v>11</v>
@@ -3710,27 +3941,30 @@
         <v>14</v>
       </c>
       <c r="G77" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H77" t="s">
-        <v>104</v>
-      </c>
-      <c r="I77">
-        <v>999</v>
+        <v>102</v>
+      </c>
+      <c r="I77" t="s">
+        <v>183</v>
       </c>
       <c r="J77" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K77" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L77">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B78" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C78" t="s">
         <v>11</v>
@@ -3745,27 +3979,30 @@
         <v>14</v>
       </c>
       <c r="G78" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H78" t="s">
-        <v>104</v>
-      </c>
-      <c r="I78">
-        <v>999</v>
+        <v>102</v>
+      </c>
+      <c r="I78" t="s">
+        <v>183</v>
       </c>
       <c r="J78" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K78" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L78">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B79" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C79" t="s">
         <v>11</v>
@@ -3780,27 +4017,30 @@
         <v>14</v>
       </c>
       <c r="G79" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H79" t="s">
-        <v>104</v>
-      </c>
-      <c r="I79">
-        <v>999</v>
+        <v>102</v>
+      </c>
+      <c r="I79" t="s">
+        <v>183</v>
       </c>
       <c r="J79" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K79" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L79">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B80" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C80" t="s">
         <v>11</v>
@@ -3815,27 +4055,30 @@
         <v>14</v>
       </c>
       <c r="G80" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H80" t="s">
-        <v>104</v>
-      </c>
-      <c r="I80">
-        <v>999</v>
+        <v>102</v>
+      </c>
+      <c r="I80" t="s">
+        <v>183</v>
       </c>
       <c r="J80" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K80" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L80">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B81" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C81" t="s">
         <v>11</v>
@@ -3850,27 +4093,30 @@
         <v>14</v>
       </c>
       <c r="G81" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H81" t="s">
-        <v>104</v>
-      </c>
-      <c r="I81">
-        <v>999</v>
+        <v>102</v>
+      </c>
+      <c r="I81" t="s">
+        <v>183</v>
       </c>
       <c r="J81" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K81" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L81">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B82" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C82" t="s">
         <v>11</v>
@@ -3885,59 +4131,65 @@
         <v>14</v>
       </c>
       <c r="G82" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H82" t="s">
-        <v>104</v>
-      </c>
-      <c r="I82">
-        <v>999</v>
+        <v>102</v>
+      </c>
+      <c r="I82" t="s">
+        <v>183</v>
       </c>
       <c r="J82" t="s">
+        <v>171</v>
+      </c>
+      <c r="K82" t="s">
+        <v>170</v>
+      </c>
+      <c r="L82">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>131</v>
+      </c>
+      <c r="B83" t="s">
+        <v>132</v>
+      </c>
+      <c r="C83" t="s">
+        <v>48</v>
+      </c>
+      <c r="D83" t="s">
+        <v>12</v>
+      </c>
+      <c r="E83" t="s">
+        <v>14</v>
+      </c>
+      <c r="F83" t="s">
+        <v>14</v>
+      </c>
+      <c r="G83" t="s">
+        <v>14</v>
+      </c>
+      <c r="H83" t="s">
+        <v>14</v>
+      </c>
+      <c r="J83" t="s">
         <v>173</v>
       </c>
-      <c r="K82" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+      <c r="K83" t="s">
+        <v>170</v>
+      </c>
+      <c r="L83" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
         <v>133</v>
       </c>
-      <c r="B83" t="s">
-        <v>134</v>
-      </c>
-      <c r="C83" t="s">
-        <v>49</v>
-      </c>
-      <c r="D83" t="s">
-        <v>12</v>
-      </c>
-      <c r="E83" t="s">
-        <v>14</v>
-      </c>
-      <c r="F83" t="s">
-        <v>14</v>
-      </c>
-      <c r="G83" t="s">
-        <v>14</v>
-      </c>
-      <c r="H83" t="s">
-        <v>14</v>
-      </c>
-      <c r="J83" t="s">
-        <v>185</v>
-      </c>
-      <c r="K83" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>135</v>
-      </c>
       <c r="B84" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C84" t="s">
         <v>11</v>
@@ -3949,30 +4201,33 @@
         <v>13</v>
       </c>
       <c r="F84" t="s">
-        <v>14</v>
+        <v>185</v>
       </c>
       <c r="G84" t="s">
         <v>15</v>
       </c>
-      <c r="H84" t="s">
-        <v>100</v>
-      </c>
-      <c r="I84">
-        <v>99</v>
+      <c r="H84" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I84" t="s">
+        <v>179</v>
       </c>
       <c r="J84" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K84" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L84">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B85" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C85" t="s">
         <v>11</v>
@@ -3987,27 +4242,30 @@
         <v>14</v>
       </c>
       <c r="G85" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H85" t="s">
         <v>16</v>
       </c>
-      <c r="I85">
-        <v>9999</v>
+      <c r="I85" t="s">
+        <v>186</v>
       </c>
       <c r="J85" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K85" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L85">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B86" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C86" t="s">
         <v>34</v>
@@ -4028,18 +4286,21 @@
         <v>14</v>
       </c>
       <c r="J86" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="K86" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L86">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B87" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C87" t="s">
         <v>11</v>
@@ -4054,42 +4315,45 @@
         <v>14</v>
       </c>
       <c r="G87" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H87" t="s">
         <v>16</v>
       </c>
-      <c r="I87">
-        <v>99999</v>
+      <c r="I87" t="s">
+        <v>177</v>
       </c>
       <c r="J87" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K87" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L87">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B88" t="s">
+        <v>141</v>
+      </c>
+      <c r="C88" t="s">
+        <v>11</v>
+      </c>
+      <c r="D88" t="s">
+        <v>12</v>
+      </c>
+      <c r="E88" t="s">
+        <v>66</v>
+      </c>
+      <c r="F88" t="s">
+        <v>142</v>
+      </c>
+      <c r="G88" t="s">
         <v>143</v>
-      </c>
-      <c r="C88" t="s">
-        <v>11</v>
-      </c>
-      <c r="D88" t="s">
-        <v>12</v>
-      </c>
-      <c r="E88" t="s">
-        <v>67</v>
-      </c>
-      <c r="F88" t="s">
-        <v>144</v>
-      </c>
-      <c r="G88" t="s">
-        <v>145</v>
       </c>
       <c r="H88" t="s">
         <v>16</v>
@@ -4098,50 +4362,56 @@
         <v>999</v>
       </c>
       <c r="J88" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="K88" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L88" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B89" t="s">
+        <v>144</v>
+      </c>
+      <c r="C89" t="s">
+        <v>48</v>
+      </c>
+      <c r="D89" t="s">
+        <v>12</v>
+      </c>
+      <c r="E89" t="s">
+        <v>14</v>
+      </c>
+      <c r="F89" t="s">
+        <v>14</v>
+      </c>
+      <c r="G89" t="s">
+        <v>14</v>
+      </c>
+      <c r="H89" t="s">
+        <v>14</v>
+      </c>
+      <c r="J89" t="s">
+        <v>173</v>
+      </c>
+      <c r="K89" t="s">
+        <v>170</v>
+      </c>
+      <c r="L89" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>145</v>
+      </c>
+      <c r="B90" t="s">
         <v>146</v>
-      </c>
-      <c r="C89" t="s">
-        <v>49</v>
-      </c>
-      <c r="D89" t="s">
-        <v>12</v>
-      </c>
-      <c r="E89" t="s">
-        <v>14</v>
-      </c>
-      <c r="F89" t="s">
-        <v>14</v>
-      </c>
-      <c r="G89" t="s">
-        <v>14</v>
-      </c>
-      <c r="H89" t="s">
-        <v>14</v>
-      </c>
-      <c r="J89" t="s">
-        <v>185</v>
-      </c>
-      <c r="K89" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>147</v>
-      </c>
-      <c r="B90" t="s">
-        <v>148</v>
       </c>
       <c r="C90" t="s">
         <v>11</v>
@@ -4153,7 +4423,7 @@
         <v>20</v>
       </c>
       <c r="F90" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G90" t="s">
         <v>14</v>
@@ -4168,15 +4438,18 @@
         <v>188</v>
       </c>
       <c r="K90" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L90">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B91" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C91" t="s">
         <v>11</v>
@@ -4188,7 +4461,7 @@
         <v>20</v>
       </c>
       <c r="F91" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G91" t="s">
         <v>14</v>
@@ -4203,15 +4476,18 @@
         <v>188</v>
       </c>
       <c r="K91" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L91">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B92" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C92" t="s">
         <v>11</v>
@@ -4223,7 +4499,7 @@
         <v>20</v>
       </c>
       <c r="F92" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G92" t="s">
         <v>14</v>
@@ -4238,15 +4514,18 @@
         <v>188</v>
       </c>
       <c r="K92" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L92">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B93" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C93" t="s">
         <v>11</v>
@@ -4258,7 +4537,7 @@
         <v>20</v>
       </c>
       <c r="F93" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G93" t="s">
         <v>14</v>
@@ -4273,15 +4552,18 @@
         <v>188</v>
       </c>
       <c r="K93" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L93">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B94" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C94" t="s">
         <v>11</v>
@@ -4293,7 +4575,7 @@
         <v>20</v>
       </c>
       <c r="F94" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G94" t="s">
         <v>14</v>
@@ -4308,15 +4590,18 @@
         <v>188</v>
       </c>
       <c r="K94" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L94">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B95" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C95" t="s">
         <v>11</v>
@@ -4328,7 +4613,7 @@
         <v>20</v>
       </c>
       <c r="F95" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G95" t="s">
         <v>14</v>
@@ -4343,15 +4628,18 @@
         <v>188</v>
       </c>
       <c r="K95" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L95">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B96" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C96" t="s">
         <v>11</v>
@@ -4363,7 +4651,7 @@
         <v>20</v>
       </c>
       <c r="F96" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G96" t="s">
         <v>14</v>
@@ -4378,15 +4666,18 @@
         <v>188</v>
       </c>
       <c r="K96" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L96">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B97" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C97" t="s">
         <v>11</v>
@@ -4398,7 +4689,7 @@
         <v>20</v>
       </c>
       <c r="F97" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G97" t="s">
         <v>14</v>
@@ -4413,15 +4704,18 @@
         <v>188</v>
       </c>
       <c r="K97" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L97">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B98" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C98" t="s">
         <v>11</v>
@@ -4433,7 +4727,7 @@
         <v>20</v>
       </c>
       <c r="F98" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G98" t="s">
         <v>14</v>
@@ -4448,15 +4742,18 @@
         <v>188</v>
       </c>
       <c r="K98" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L98">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B99" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C99" t="s">
         <v>11</v>
@@ -4465,33 +4762,36 @@
         <v>12</v>
       </c>
       <c r="E99" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F99" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G99" t="s">
         <v>14</v>
       </c>
       <c r="H99" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I99">
         <v>1000</v>
       </c>
       <c r="J99" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K99" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L99">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B100" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C100" t="s">
         <v>11</v>
@@ -4500,33 +4800,36 @@
         <v>12</v>
       </c>
       <c r="E100" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F100" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G100" t="s">
         <v>14</v>
       </c>
       <c r="H100" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I100">
         <v>1000</v>
       </c>
       <c r="J100" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K100" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L100">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B101" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C101" t="s">
         <v>11</v>
@@ -4535,10 +4838,10 @@
         <v>12</v>
       </c>
       <c r="E101" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F101" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G101" t="s">
         <v>14</v>
@@ -4550,18 +4853,21 @@
         <v>1000</v>
       </c>
       <c r="J101" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K101" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L101">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B102" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C102" t="s">
         <v>11</v>
@@ -4570,10 +4876,10 @@
         <v>12</v>
       </c>
       <c r="E102" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F102" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G102" t="s">
         <v>14</v>
@@ -4585,18 +4891,21 @@
         <v>1000</v>
       </c>
       <c r="J102" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K102" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L102">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B103" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C103" t="s">
         <v>11</v>
@@ -4605,10 +4914,10 @@
         <v>12</v>
       </c>
       <c r="E103" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F103" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G103" t="s">
         <v>14</v>
@@ -4620,18 +4929,21 @@
         <v>1000</v>
       </c>
       <c r="J103" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K103" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L103">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B104" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C104" t="s">
         <v>11</v>
@@ -4640,10 +4952,10 @@
         <v>12</v>
       </c>
       <c r="E104" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F104" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G104" t="s">
         <v>14</v>
@@ -4655,18 +4967,21 @@
         <v>1000</v>
       </c>
       <c r="J104" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K104" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L104">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B105" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C105" t="s">
         <v>11</v>
@@ -4675,10 +4990,10 @@
         <v>12</v>
       </c>
       <c r="E105" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F105" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G105" t="s">
         <v>14</v>
@@ -4690,18 +5005,21 @@
         <v>1000</v>
       </c>
       <c r="J105" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K105" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L105">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B106" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C106" t="s">
         <v>11</v>
@@ -4710,10 +5028,10 @@
         <v>12</v>
       </c>
       <c r="E106" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F106" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G106" t="s">
         <v>14</v>
@@ -4725,18 +5043,21 @@
         <v>1000</v>
       </c>
       <c r="J106" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K106" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="L106">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B107" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C107" t="s">
         <v>11</v>
@@ -4745,10 +5066,10 @@
         <v>12</v>
       </c>
       <c r="E107" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F107" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G107" t="s">
         <v>14</v>
@@ -4760,13 +5081,17 @@
         <v>1000</v>
       </c>
       <c r="J107" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K107" t="s">
-        <v>172</v>
+        <v>170</v>
+      </c>
+      <c r="L107">
+        <v>224</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
